--- a/artfynd/S 4959-2024 artfynd.xlsx
+++ b/artfynd/S 4959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,244 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135300679</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lindbäcken, Västergundsjö, Västergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>679863</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7038998</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135300163</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lindbäcken, Västergundsjö, Västergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679829</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7038998</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 4959-2024 artfynd.xlsx
+++ b/artfynd/S 4959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108076734</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,8 +1038,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 4959-2024 artfynd.xlsx
+++ b/artfynd/S 4959-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>135300679</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135300163</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 4959-2024 artfynd.xlsx
+++ b/artfynd/S 4959-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>135300679</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135300163</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 4959-2024 artfynd.xlsx
+++ b/artfynd/S 4959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,9 +796,259 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135300679</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lindbäcken, Västergundsjö, Västergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>679863</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7038998</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300679</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135300163</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lindbäcken, Västergundsjö, Västergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679829</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7038998</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300163</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 4959-2024 artfynd.xlsx
+++ b/artfynd/S 4959-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>135300679</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135300163</v>
       </c>
       <c r="B4" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
